--- a/output7/【河洛文讀注音-方音符號】《涼州詞》.xlsx
+++ b/output7/【河洛文讀注音-方音符號】《涼州詞》.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F380B91-20EC-4E3B-A7BE-4826CA4AFF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0B74FFF-0BB3-44C0-A91B-62941D0C47EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="1095" windowWidth="21420" windowHeight="13620" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="1295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="1300">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4453,6 +4453,25 @@
   <si>
     <t>ㄍㄨㄢ</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漢字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台語音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>校正音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>座標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【河洛文讀注音-方音符號】《涼州詞》.xlsx</t>
   </si>
 </sst>
 </file>
@@ -4851,7 +4870,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5035,9 +5054,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6840,7 +6856,9 @@
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>1299</v>
+      </c>
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="4" t="s">
@@ -7002,16 +7020,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>1295</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>1296</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>1297</v>
       </c>
       <c r="D1" t="s">
-        <v>498</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7517,16 +7535,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>1295</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>1296</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>1297</v>
       </c>
       <c r="D1" t="s">
-        <v>498</v>
+        <v>1298</v>
       </c>
     </row>
   </sheetData>
@@ -7542,16 +7560,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>1295</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>1296</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>1297</v>
       </c>
       <c r="D1" t="s">
-        <v>498</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7701,31 +7719,31 @@
       <c r="B5" s="19">
         <v>1</v>
       </c>
-      <c r="D5" s="61" t="s">
+      <c r="D5" s="39" t="s">
         <v>1166</v>
       </c>
-      <c r="E5" s="61" t="s">
+      <c r="E5" s="39" t="s">
         <v>1167</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F5" s="39" t="s">
         <v>1168</v>
       </c>
-      <c r="G5" s="61" t="s">
+      <c r="G5" s="39" t="s">
         <v>1169</v>
       </c>
-      <c r="H5" s="61" t="s">
+      <c r="H5" s="39" t="s">
         <v>1170</v>
       </c>
-      <c r="I5" s="61" t="s">
+      <c r="I5" s="39" t="s">
         <v>1171</v>
       </c>
-      <c r="J5" s="61" t="s">
+      <c r="J5" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="K5" s="61" t="s">
+      <c r="K5" s="39" t="s">
         <v>1172</v>
       </c>
-      <c r="L5" s="61" t="str">
+      <c r="L5" s="39" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -7832,31 +7850,31 @@
         <f>B5+1</f>
         <v>2</v>
       </c>
-      <c r="D9" s="61" t="s">
+      <c r="D9" s="39" t="s">
         <v>1173</v>
       </c>
-      <c r="E9" s="61" t="s">
+      <c r="E9" s="39" t="s">
         <v>1174</v>
       </c>
-      <c r="F9" s="61" t="s">
+      <c r="F9" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="G9" s="61" t="s">
+      <c r="G9" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="61" t="s">
+      <c r="H9" s="39" t="s">
         <v>1175</v>
       </c>
-      <c r="I9" s="61" t="s">
+      <c r="I9" s="39" t="s">
         <v>1176</v>
       </c>
-      <c r="J9" s="61" t="s">
+      <c r="J9" s="39" t="s">
         <v>1177</v>
       </c>
-      <c r="K9" s="61" t="s">
+      <c r="K9" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="61" t="str">
+      <c r="L9" s="39" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -7964,31 +7982,31 @@
         <f>B9+1</f>
         <v>3</v>
       </c>
-      <c r="D13" s="61" t="s">
+      <c r="D13" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="61" t="s">
+      <c r="E13" s="39" t="s">
         <v>1178</v>
       </c>
-      <c r="F13" s="61" t="s">
+      <c r="F13" s="39" t="s">
         <v>1179</v>
       </c>
-      <c r="G13" s="61" t="s">
+      <c r="G13" s="39" t="s">
         <v>1180</v>
       </c>
-      <c r="H13" s="61" t="s">
+      <c r="H13" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="I13" s="61" t="s">
+      <c r="I13" s="39" t="s">
         <v>1181</v>
       </c>
-      <c r="J13" s="61" t="s">
+      <c r="J13" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="K13" s="61" t="s">
+      <c r="K13" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="L13" s="61" t="str">
+      <c r="L13" s="39" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -8097,31 +8115,31 @@
         <f>B13+1</f>
         <v>4</v>
       </c>
-      <c r="D17" s="61" t="s">
+      <c r="D17" s="39" t="s">
         <v>1182</v>
       </c>
-      <c r="E17" s="61" t="s">
+      <c r="E17" s="39" t="s">
         <v>1183</v>
       </c>
-      <c r="F17" s="61" t="s">
+      <c r="F17" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="G17" s="61" t="s">
+      <c r="G17" s="39" t="s">
         <v>1184</v>
       </c>
-      <c r="H17" s="61" t="s">
+      <c r="H17" s="39" t="s">
         <v>1185</v>
       </c>
-      <c r="I17" s="61" t="s">
+      <c r="I17" s="39" t="s">
         <v>1186</v>
       </c>
-      <c r="J17" s="61" t="s">
+      <c r="J17" s="39" t="s">
         <v>1187</v>
       </c>
-      <c r="K17" s="61" t="s">
+      <c r="K17" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="61" t="str">
+      <c r="L17" s="39" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -8228,31 +8246,31 @@
         <f>B17+1</f>
         <v>5</v>
       </c>
-      <c r="D21" s="61" t="s">
+      <c r="D21" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="61" t="s">
+      <c r="E21" s="39" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="61" t="s">
+      <c r="F21" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="G21" s="61" t="s">
+      <c r="G21" s="39" t="s">
         <v>1188</v>
       </c>
-      <c r="H21" s="61" t="s">
+      <c r="H21" s="39" t="s">
         <v>1189</v>
       </c>
-      <c r="I21" s="61" t="s">
+      <c r="I21" s="39" t="s">
         <v>1190</v>
       </c>
-      <c r="J21" s="61" t="s">
+      <c r="J21" s="39" t="s">
         <v>1191</v>
       </c>
-      <c r="K21" s="61" t="s">
+      <c r="K21" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="L21" s="61" t="str">
+      <c r="L21" s="39" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -8345,7 +8363,7 @@
         <f>B21+1</f>
         <v>6</v>
       </c>
-      <c r="D25" s="61" t="s">
+      <c r="D25" s="39" t="s">
         <v>38</v>
       </c>
       <c r="E25" s="39"/>
